--- a/cuentas y gastos.xlsx
+++ b/cuentas y gastos.xlsx
@@ -5,21 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LEGION LOCAL TORRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFC2DC0B-1C23-448B-894E-E727385C66BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDF1F48-60A5-4388-9627-3390ED8B12DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32184FBB-0CFE-4A0C-9B5C-F2EB776C1F94}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="MAYO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$F$7:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MAYO!$F$7:$H$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="23">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -40,9 +39,6 @@
     <t>CORTE</t>
   </si>
   <si>
-    <t>MAYO</t>
-  </si>
-  <si>
     <t>OBSERVACIONES</t>
   </si>
   <si>
@@ -80,17 +76,79 @@
   </si>
   <si>
     <t>RETORNOS</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Pago Moto </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                                                         ①②③④⑤⑥⑦⑧</t>
+    </r>
+  </si>
+  <si>
+    <t>385,000 COP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                          DESCRIPCION                                                                               CUOTA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Celular  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                                                              ①②③④⑤⑥⑦⑧</t>
+    </r>
+  </si>
+  <si>
+    <t>160,000 COP</t>
+  </si>
+  <si>
+    <t>000,000 COP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="dd\-mm\-yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +165,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -192,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -441,12 +506,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -458,9 +561,105 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -470,189 +669,125 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -981,7 +1116,7 @@
   <sheetData>
     <row r="3" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C3" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="6">
         <v>50000</v>
@@ -989,7 +1124,7 @@
     </row>
     <row r="4" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C4" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="6">
         <v>50000</v>
@@ -997,7 +1132,7 @@
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C5" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6">
         <v>50000</v>
@@ -1005,464 +1140,572 @@
     </row>
     <row r="6" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="27"/>
+      <c r="J7" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
-      <c r="J7" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="62"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="49"/>
     </row>
     <row r="8" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="30"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="52"/>
     </row>
     <row r="9" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="54" t="s">
+      <c r="C9" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="55"/>
+      <c r="H9" s="17"/>
       <c r="J9" s="66" t="s">
         <v>0</v>
       </c>
       <c r="K9" s="67"/>
       <c r="L9" s="67"/>
       <c r="M9" s="68"/>
-      <c r="N9" s="18" t="s">
+      <c r="N9" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="O9" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="12" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="10" spans="3:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="56">
-        <v>15</v>
-      </c>
-      <c r="H10" s="58">
+      <c r="C10" s="61"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="18">
+        <v>15</v>
+      </c>
+      <c r="H10" s="20">
         <v>30</v>
       </c>
       <c r="J10" s="69"/>
       <c r="K10" s="70"/>
       <c r="L10" s="70"/>
       <c r="M10" s="71"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="13"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="45"/>
     </row>
     <row r="11" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="59"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="21"/>
       <c r="J11" s="72"/>
       <c r="K11" s="73"/>
       <c r="L11" s="73"/>
       <c r="M11" s="74"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="14"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="46"/>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="J12" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="76"/>
+      <c r="L12" s="76"/>
+      <c r="M12" s="77"/>
+      <c r="N12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="J13" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
+      <c r="J15" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
+      <c r="J16" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
+      <c r="J17" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
+      <c r="J18" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+      <c r="J19" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
+      <c r="J20" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
+      <c r="J21" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
+      <c r="J22" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="23" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C23" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="15">
+      <c r="C23" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="22">
         <v>0</v>
       </c>
-      <c r="H23" s="17"/>
+      <c r="H23" s="24"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11">
+      <c r="J23" s="15">
         <v>0</v>
       </c>
-      <c r="O23" s="11"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15">
+        <v>0</v>
+      </c>
+      <c r="O23" s="15"/>
     </row>
     <row r="24" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="27"/>
+      <c r="J25" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" s="54"/>
+      <c r="L25" s="55"/>
+    </row>
+    <row r="26" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="30"/>
+      <c r="J26" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="57"/>
+      <c r="L26" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C27" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
-      <c r="J25" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="K25" s="23"/>
-      <c r="L25" s="24"/>
-    </row>
-    <row r="26" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="30"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
-      <c r="J26" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="26"/>
-      <c r="L26" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C27" s="41" t="s">
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="18" t="s">
+      <c r="H27" s="44" t="s">
         <v>11</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>12</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
     </row>
     <row r="28" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="44"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="13"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="45"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
     </row>
     <row r="29" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="14"/>
+      <c r="C29" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="46"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
+    <row r="30" spans="3:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C30" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="80">
+        <v>46183</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="1"/>
+    <row r="31" spans="3:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C31" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="79"/>
+      <c r="E31" s="79"/>
+      <c r="F31" s="79"/>
+      <c r="G31" s="81" t="s">
+        <v>21</v>
+      </c>
       <c r="H31" s="1"/>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="1"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H32" s="1"/>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="1"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H33" s="1"/>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="1"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H34" s="1"/>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="1"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H35" s="1"/>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="1"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H36" s="1"/>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="15"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="1"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H37" s="1"/>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="1"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H38" s="1"/>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="1"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H39" s="1"/>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="1"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="81" t="s">
+        <v>22</v>
+      </c>
       <c r="H40" s="1"/>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C41" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="15">
+      <c r="C41" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="22">
         <v>0</v>
       </c>
-      <c r="H41" s="17"/>
+      <c r="H41" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="J9:M11"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="H27:H29"/>
+    <mergeCell ref="J7:O8"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="C7:H8"/>
+    <mergeCell ref="C9:F10"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C41:F41"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C25:H26"/>
     <mergeCell ref="C27:F28"/>
@@ -1479,34 +1722,21 @@
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="J7:O8"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="C7:H8"/>
-    <mergeCell ref="C9:F10"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="J9:M11"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>